--- a/data/trans_orig/P16A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487612</t>
+          <t>487576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448232</t>
+          <t>448860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461608</t>
+          <t>461512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>938990</t>
+          <t>939759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>953741</t>
+          <t>954027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713929</t>
+          <t>713915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728312</t>
+          <t>728172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607482</t>
+          <t>606917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620492</t>
+          <t>620421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1326406</t>
+          <t>1327499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1345446</t>
+          <t>1345542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>39239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>620796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633856</t>
+          <t>633827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650683</t>
+          <t>650505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672320</t>
+          <t>671468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277996</t>
+          <t>1277380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302008</t>
+          <t>1302995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38343</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67041</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493826</t>
+          <t>493141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>509945</t>
+          <t>510114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>468347</t>
+          <t>466741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490375</t>
+          <t>490864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>967748</t>
+          <t>968736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>996446</t>
+          <t>997843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43151</t>
+          <t>42717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34902</t>
+          <t>35445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61997</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359633</t>
+          <t>360431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377164</t>
+          <t>377048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>360835</t>
+          <t>361269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382250</t>
+          <t>382604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>728699</t>
+          <t>726900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>755794</t>
+          <t>755251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>49877</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>65896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269129</t>
+          <t>269079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283784</t>
+          <t>283980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294041</t>
+          <t>293057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315670</t>
+          <t>315340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569884</t>
+          <t>569621</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595697</t>
+          <t>595277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38421</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>56054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>187202</t>
+          <t>186681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201501</t>
+          <t>200950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295487</t>
+          <t>295669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316273</t>
+          <t>315881</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>488175</t>
+          <t>487737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513189</t>
+          <t>514388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>103312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155861</t>
+          <t>155481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207406</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>235596</t>
+          <t>233080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301929</t>
+          <t>297133</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3170464</t>
+          <t>3172213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3207315</t>
+          <t>3207718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3171791</t>
+          <t>3171745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3223336</t>
+          <t>3223716</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6352793</t>
+          <t>6357589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6419126</t>
+          <t>6421642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446330</t>
+          <t>446300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419597</t>
+          <t>419642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428347</t>
+          <t>428342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869593</t>
+          <t>869956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879678</t>
+          <t>879772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48280</t>
+          <t>46662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658848</t>
+          <t>658487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677558</t>
+          <t>677552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584028</t>
+          <t>583919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600759</t>
+          <t>600555</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1247171</t>
+          <t>1248789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1274753</t>
+          <t>1274443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31696</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30338</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45350</t>
+          <t>46321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78400</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648358</t>
+          <t>648100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668104</t>
+          <t>668102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651058</t>
+          <t>652218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676580</t>
+          <t>678001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1308572</t>
+          <t>1309880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1341622</t>
+          <t>1340651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>39212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40318</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>69277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>63893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99854</t>
+          <t>101050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576534</t>
+          <t>575405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597903</t>
+          <t>597629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>544554</t>
+          <t>544931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573890</t>
+          <t>573682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1128971</t>
+          <t>1127775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165978</t>
+          <t>1164932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>62443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49825</t>
+          <t>49734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>78331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405038</t>
+          <t>404708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419910</t>
+          <t>420182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>384710</t>
+          <t>385357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411254</t>
+          <t>410845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797228</t>
+          <t>797813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>826319</t>
+          <t>826410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42269</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>71090</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282240</t>
+          <t>282470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300720</t>
+          <t>300599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>302903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323786</t>
+          <t>324442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>590266</t>
+          <t>591755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>620576</t>
+          <t>620025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39931</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66781</t>
+          <t>67485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55189</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90309</t>
+          <t>88360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215905</t>
+          <t>217671</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238042</t>
+          <t>238170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319972</t>
+          <t>319268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346822</t>
+          <t>348169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>545480</t>
+          <t>547429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>580600</t>
+          <t>579710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92671</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137543</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>225291</t>
+          <t>220617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>283634</t>
+          <t>285627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>329798</t>
+          <t>329289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>410502</t>
+          <t>410329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3283636</t>
+          <t>3279993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3328508</t>
+          <t>3326799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3263658</t>
+          <t>3261665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3322001</t>
+          <t>3326675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6557969</t>
+          <t>6558142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6638673</t>
+          <t>6639182</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411082</t>
+          <t>410599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379602</t>
+          <t>379023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391744</t>
+          <t>392081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794982</t>
+          <t>795195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>809823</t>
+          <t>809296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571219</t>
+          <t>571415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584550</t>
+          <t>584557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540487</t>
+          <t>541527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555115</t>
+          <t>555272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1118174</t>
+          <t>1118021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1137139</t>
+          <t>1137080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25923</t>
+          <t>26215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638406</t>
+          <t>638417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657223</t>
+          <t>656948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612630</t>
+          <t>612001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>635463</t>
+          <t>635171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258800</t>
+          <t>1258336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287804</t>
+          <t>1287389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>36896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66694</t>
+          <t>65928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93854</t>
+          <t>94580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607227</t>
+          <t>609152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628659</t>
+          <t>629035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582383</t>
+          <t>583149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612095</t>
+          <t>611179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1201271</t>
+          <t>1200545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1235557</t>
+          <t>1235821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42579</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50906</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>80593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77874</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117304</t>
+          <t>118245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435339</t>
+          <t>434280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>458427</t>
+          <t>457247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413697</t>
+          <t>416256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445943</t>
+          <t>445498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>857463</t>
+          <t>856522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>896893</t>
+          <t>897308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61378</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47103</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76583</t>
+          <t>77420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312031</t>
+          <t>311979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326664</t>
+          <t>326485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316384</t>
+          <t>315446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341616</t>
+          <t>343205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635509</t>
+          <t>634672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>664989</t>
+          <t>664706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64443</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>49979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81353</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233385</t>
+          <t>233029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247764</t>
+          <t>246928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>335726</t>
+          <t>334964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>363777</t>
+          <t>366107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>575814</t>
+          <t>574320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>608249</t>
+          <t>607188</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100365</t>
+          <t>97572</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144005</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238343</t>
+          <t>240366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>303133</t>
+          <t>304472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>348475</t>
+          <t>350080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>426976</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3250345</t>
+          <t>3253843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3293985</t>
+          <t>3296778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3241409</t>
+          <t>3240070</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3306199</t>
+          <t>3304176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6511916</t>
+          <t>6509800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6590417</t>
+          <t>6588812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14641</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2536</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2536</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>12726</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300081</t>
+          <t>298559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>700461</t>
+          <t>702421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26757</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407197</t>
+          <t>408403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421741</t>
+          <t>421927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493272</t>
+          <t>493431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508064</t>
+          <t>507910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908294</t>
+          <t>907432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927129</t>
+          <t>926787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59452</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508395</t>
+          <t>509582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525483</t>
+          <t>525747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505373</t>
+          <t>505000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522888</t>
+          <t>522448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1019354</t>
+          <t>1021288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044253</t>
+          <t>1044924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68149</t>
+          <t>68190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78593</t>
+          <t>77924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>63594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132255</t>
+          <t>134940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819637</t>
+          <t>819596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871424</t>
+          <t>869980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634288</t>
+          <t>634957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666586</t>
+          <t>666707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1468412</t>
+          <t>1465727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1542304</t>
+          <t>1537073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79835</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114288</t>
+          <t>115695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515490</t>
+          <t>516191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536237</t>
+          <t>536739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>464434</t>
+          <t>465061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487841</t>
+          <t>488002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>990218</t>
+          <t>988811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1019634</t>
+          <t>1020570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85926</t>
+          <t>86729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98861</t>
+          <t>98757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>342063</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355564</t>
+          <t>355495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>522442</t>
+          <t>521639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>586736</t>
+          <t>586151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877672</t>
+          <t>877776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>935700</t>
+          <t>938074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>31456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82332</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>81359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107886</t>
+          <t>106684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250781</t>
+          <t>250813</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265804</t>
+          <t>265518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>342062</t>
+          <t>341856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>364193</t>
+          <t>364587</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>598777</t>
+          <t>599979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625022</t>
+          <t>625304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>114257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>169391</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>240418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>325044</t>
+          <t>327373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376179</t>
+          <t>373970</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>481945</t>
+          <t>479385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3288939</t>
+          <t>3288726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3347192</t>
+          <t>3344073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3332040</t>
+          <t>3329711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3425724</t>
+          <t>3416666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6633469</t>
+          <t>6636029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6739235</t>
+          <t>6741444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487576</t>
+          <t>487499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448860</t>
+          <t>447847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461512</t>
+          <t>461922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>939759</t>
+          <t>939721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>954027</t>
+          <t>954102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713915</t>
+          <t>713209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728172</t>
+          <t>727939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>606917</t>
+          <t>607005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620421</t>
+          <t>620400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1327499</t>
+          <t>1325102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1345542</t>
+          <t>1345573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>49612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620796</t>
+          <t>622055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633827</t>
+          <t>633998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650505</t>
+          <t>651414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671468</t>
+          <t>671761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277380</t>
+          <t>1277782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302995</t>
+          <t>1301876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>46800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66053</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493141</t>
+          <t>493783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510114</t>
+          <t>510685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>466741</t>
+          <t>468842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490864</t>
+          <t>490871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>968736</t>
+          <t>967694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>997843</t>
+          <t>997483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>43411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360431</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377048</t>
+          <t>376568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361269</t>
+          <t>360575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382604</t>
+          <t>382085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>726900</t>
+          <t>727456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>755251</t>
+          <t>753934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>39998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>66349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269079</t>
+          <t>268839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283980</t>
+          <t>284003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293057</t>
+          <t>292898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315340</t>
+          <t>315488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569621</t>
+          <t>569168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595277</t>
+          <t>595519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>39301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>30219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>57074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186681</t>
+          <t>186626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200950</t>
+          <t>201532</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295669</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315881</t>
+          <t>315730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487737</t>
+          <t>486717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514388</t>
+          <t>513572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207452</t>
+          <t>205573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>233080</t>
+          <t>232017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>294823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3172213</t>
+          <t>3170629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3207718</t>
+          <t>3206292</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3171745</t>
+          <t>3173624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3223716</t>
+          <t>3226168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6357589</t>
+          <t>6359899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6421642</t>
+          <t>6422705</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446300</t>
+          <t>445392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452290</t>
+          <t>452294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419642</t>
+          <t>419521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428342</t>
+          <t>428345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869956</t>
+          <t>870438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879772</t>
+          <t>879525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46662</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658487</t>
+          <t>657484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677552</t>
+          <t>677157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>583919</t>
+          <t>584160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600555</t>
+          <t>600975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1248789</t>
+          <t>1250010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1274443</t>
+          <t>1274665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>45785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
+          <t>78260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648100</t>
+          <t>646924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668102</t>
+          <t>667971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652218</t>
+          <t>653354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678001</t>
+          <t>678019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309880</t>
+          <t>1308712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1340651</t>
+          <t>1341187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39212</t>
+          <t>38761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69277</t>
+          <t>70348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63893</t>
+          <t>62899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101050</t>
+          <t>100164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>575856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597629</t>
+          <t>597683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>544931</t>
+          <t>543860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573682</t>
+          <t>573802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127775</t>
+          <t>1128661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164932</t>
+          <t>1165926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62443</t>
+          <t>62971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>49287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>81588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>404708</t>
+          <t>404063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420182</t>
+          <t>419870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385357</t>
+          <t>384829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410845</t>
+          <t>412140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797813</t>
+          <t>794556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>826410</t>
+          <t>826857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>51802</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42820</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71090</t>
+          <t>70945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282470</t>
+          <t>282097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300599</t>
+          <t>300560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302903</t>
+          <t>301257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324442</t>
+          <t>324876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>591755</t>
+          <t>591900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>620025</t>
+          <t>621660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31365</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38584</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>68012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56079</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88360</t>
+          <t>89658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217671</t>
+          <t>217510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238170</t>
+          <t>237652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319268</t>
+          <t>318741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348169</t>
+          <t>348417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547429</t>
+          <t>546131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>579710</t>
+          <t>580286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94380</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220617</t>
+          <t>222140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>285627</t>
+          <t>287276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>329289</t>
+          <t>330772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>410329</t>
+          <t>412982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3279993</t>
+          <t>3282764</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3326799</t>
+          <t>3330045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3261665</t>
+          <t>3260016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3326675</t>
+          <t>3325152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6558142</t>
+          <t>6555489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6639182</t>
+          <t>6637699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410599</t>
+          <t>411320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379023</t>
+          <t>379818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>392081</t>
+          <t>392102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>795195</t>
+          <t>795930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>809296</t>
+          <t>810473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>23762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571415</t>
+          <t>571638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584557</t>
+          <t>584619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>541527</t>
+          <t>539782</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555272</t>
+          <t>555083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1118021</t>
+          <t>1118780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1137080</t>
+          <t>1137009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>50380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72147</t>
+          <t>71715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638417</t>
+          <t>636943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656948</t>
+          <t>656805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612001</t>
+          <t>611006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>635171</t>
+          <t>635063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258336</t>
+          <t>1258768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287389</t>
+          <t>1287542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>36557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65928</t>
+          <t>66296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>94965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609152</t>
+          <t>608523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629035</t>
+          <t>628865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583149</t>
+          <t>582781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611179</t>
+          <t>612520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200545</t>
+          <t>1200160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1235821</t>
+          <t>1235411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118245</t>
+          <t>115514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434280</t>
+          <t>435724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457247</t>
+          <t>457410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416256</t>
+          <t>414313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445498</t>
+          <t>446287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>856522</t>
+          <t>859253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>897308</t>
+          <t>896984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62316</t>
+          <t>61664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47386</t>
+          <t>46673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>79693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311979</t>
+          <t>311805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326485</t>
+          <t>326957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315446</t>
+          <t>316098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>343205</t>
+          <t>342344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>634672</t>
+          <t>632399</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>664706</t>
+          <t>665419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>35201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>66241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49979</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82847</t>
+          <t>82400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233029</t>
+          <t>232736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246928</t>
+          <t>247617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>334964</t>
+          <t>333928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>366107</t>
+          <t>364968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>574320</t>
+          <t>574767</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>607188</t>
+          <t>608244</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97572</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140507</t>
+          <t>142104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240366</t>
+          <t>240175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304472</t>
+          <t>304450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350080</t>
+          <t>347022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>429092</t>
+          <t>426620</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3253843</t>
+          <t>3252246</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3296778</t>
+          <t>3294490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3240070</t>
+          <t>3240092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3304176</t>
+          <t>3304367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6509800</t>
+          <t>6512272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6588812</t>
+          <t>6591870</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310664</t>
+          <t>360064</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298559</t>
+          <t>349846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710651</t>
+          <t>767857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702421</t>
+          <t>755567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,27 +10008,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10121,22 +10121,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>417467</t>
+          <t>469588</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408403</t>
+          <t>459808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421927</t>
+          <t>473861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>502076</t>
+          <t>491193</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493431</t>
+          <t>481864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507910</t>
+          <t>496373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>919542</t>
+          <t>960782</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907432</t>
+          <t>948541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926787</t>
+          <t>968523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518410</t>
+          <t>602565</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509582</t>
+          <t>590439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525747</t>
+          <t>609362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>515118</t>
+          <t>592475</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505000</t>
+          <t>582401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522448</t>
+          <t>601151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033528</t>
+          <t>1195039</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1021288</t>
+          <t>1182728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044924</t>
+          <t>1206352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>57874</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77924</t>
+          <t>70910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102705</t>
+          <t>102750</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63594</t>
+          <t>86046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134940</t>
+          <t>124344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>844119</t>
+          <t>655741</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819596</t>
+          <t>639591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869980</t>
+          <t>668747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>679012</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634957</t>
+          <t>665976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666707</t>
+          <t>690784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1497962</t>
+          <t>1334754</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1465727</t>
+          <t>1313160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1537073</t>
+          <t>1351458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>46475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56267</t>
+          <t>60759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99298</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83936</t>
+          <t>93927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115695</t>
+          <t>125830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>528008</t>
+          <t>573467</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516191</t>
+          <t>561884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536739</t>
+          <t>582677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>477201</t>
+          <t>532654</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465061</t>
+          <t>520635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>488002</t>
+          <t>546011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1005208</t>
+          <t>1106121</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>988811</t>
+          <t>1089299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1020570</t>
+          <t>1121202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544269</t>
+          <t>606770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544269</t>
+          <t>606770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544269</t>
+          <t>606770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104506</t>
+          <t>1215129</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104506</t>
+          <t>1215129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104506</t>
+          <t>1215129</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25867</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54402</t>
+          <t>61210</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>72504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>73122</t>
+          <t>81273</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>69007</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98757</t>
+          <t>94952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>349445</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>378991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355495</t>
+          <t>393667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>553966</t>
+          <t>377956</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521639</t>
+          <t>366662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>586151</t>
+          <t>387153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>903411</t>
+          <t>764973</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877776</t>
+          <t>751294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>938074</t>
+          <t>777239</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>66905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82538</t>
+          <t>93274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>94153</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81359</t>
+          <t>88871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>118939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>259180</t>
+          <t>284668</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250813</t>
+          <t>276244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265518</t>
+          <t>291727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>353331</t>
+          <t>384193</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>341856</t>
+          <t>369805</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>364587</t>
+          <t>396174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>612510</t>
+          <t>668861</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599979</t>
+          <t>653843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625304</t>
+          <t>683911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114257</t>
+          <t>128724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>169604</t>
+          <t>176451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240418</t>
+          <t>288698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>327373</t>
+          <t>344031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>428107</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>479385</t>
+          <t>501395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3316616</t>
+          <t>3380840</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3288726</t>
+          <t>3354829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3344073</t>
+          <t>3402556</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3366197</t>
+          <t>3417548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3329711</t>
+          <t>3387604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3416666</t>
+          <t>3442937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6682813</t>
+          <t>6798388</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6636029</t>
+          <t>6761520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6741444</t>
+          <t>6834808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
